--- a/Assets/Resources/Data/Excel/AccItemData.xlsx
+++ b/Assets/Resources/Data/Excel/AccItemData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26501"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\grunge\Assets\Resources\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F2B9BA5-F54A-43F8-BD09-FF4F2EB59AE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1782FBB-B075-44B3-8D54-FF387E2BEDF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{821E5210-0A25-4A4B-8AB0-920035292A79}"/>
+    <workbookView xWindow="15940" yWindow="6470" windowWidth="19200" windowHeight="13050" xr2:uid="{821E5210-0A25-4A4B-8AB0-920035292A79}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -84,6 +84,10 @@
   </si>
   <si>
     <t>Sprites/Items/Acc/nine_pilgrims_bible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>detailID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -91,7 +95,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -104,6 +108,14 @@
       <sz val="8"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
@@ -130,8 +142,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -448,10 +463,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBD9A5E5-7AC3-44DF-9A77-C3F28FD6A29D}">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -461,8 +476,11 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>1</v>
       </c>
@@ -472,8 +490,11 @@
       <c r="C2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D2" s="1">
+        <v>23020</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>2</v>
       </c>
@@ -483,8 +504,11 @@
       <c r="C3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D3" s="1">
+        <v>23021</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>3</v>
       </c>
@@ -494,8 +518,11 @@
       <c r="C4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D4" s="1">
+        <v>23022</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>4</v>
       </c>
@@ -505,8 +532,11 @@
       <c r="C5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D5" s="1">
+        <v>23023</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>5</v>
       </c>
@@ -516,8 +546,11 @@
       <c r="C6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D6" s="1">
+        <v>23024</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>6</v>
       </c>
@@ -527,8 +560,11 @@
       <c r="C7" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D7" s="1">
+        <v>23025</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>7</v>
       </c>
@@ -538,8 +574,11 @@
       <c r="C8" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D8" s="1">
+        <v>23026</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>8</v>
       </c>
@@ -549,8 +588,11 @@
       <c r="C9" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D9" s="1">
+        <v>23027</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>9</v>
       </c>
@@ -560,8 +602,11 @@
       <c r="C10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D10" s="1">
+        <v>23028</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>10</v>
       </c>
@@ -571,8 +616,11 @@
       <c r="C11" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D11" s="1">
+        <v>23029</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>11</v>
       </c>
@@ -582,8 +630,11 @@
       <c r="C12" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D12" s="1">
+        <v>23030</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>12</v>
       </c>
@@ -592,6 +643,9 @@
       </c>
       <c r="C13" t="s">
         <v>14</v>
+      </c>
+      <c r="D13" s="1">
+        <v>23031</v>
       </c>
     </row>
   </sheetData>
